--- a/artfynd/A 49099-2021 artfynd.xlsx
+++ b/artfynd/A 49099-2021 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124907483</v>
+        <v>124907602</v>
       </c>
       <c r="B2" t="n">
-        <v>79892</v>
+        <v>78810</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>479389</v>
+        <v>479392</v>
       </c>
       <c r="R2" t="n">
-        <v>6849588</v>
+        <v>6849592</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124907602</v>
+        <v>124907760</v>
       </c>
       <c r="B3" t="n">
-        <v>78810</v>
+        <v>79891</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,13 +817,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>479392</v>
+        <v>479384</v>
       </c>
       <c r="R3" t="n">
-        <v>6849592</v>
+        <v>6849692</v>
       </c>
       <c r="S3" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124907760</v>
+        <v>124907483</v>
       </c>
       <c r="B5" t="n">
-        <v>79891</v>
+        <v>79892</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -997,21 +997,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,13 +1021,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>479384</v>
+        <v>479389</v>
       </c>
       <c r="R5" t="n">
-        <v>6849692</v>
+        <v>6849588</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>

--- a/artfynd/A 49099-2021 artfynd.xlsx
+++ b/artfynd/A 49099-2021 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124907602</v>
+        <v>124907483</v>
       </c>
       <c r="B2" t="n">
-        <v>78810</v>
+        <v>79892</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>479392</v>
+        <v>479389</v>
       </c>
       <c r="R2" t="n">
-        <v>6849592</v>
+        <v>6849588</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124907760</v>
+        <v>124907200</v>
       </c>
       <c r="B3" t="n">
-        <v>79891</v>
+        <v>78810</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,13 +817,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>479384</v>
+        <v>479211</v>
       </c>
       <c r="R3" t="n">
-        <v>6849692</v>
+        <v>6849504</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124907200</v>
+        <v>124907760</v>
       </c>
       <c r="B4" t="n">
-        <v>78810</v>
+        <v>79891</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,21 +895,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,13 +919,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>479211</v>
+        <v>479384</v>
       </c>
       <c r="R4" t="n">
-        <v>6849504</v>
+        <v>6849692</v>
       </c>
       <c r="S4" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124907483</v>
+        <v>124907602</v>
       </c>
       <c r="B5" t="n">
-        <v>79892</v>
+        <v>78810</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -997,21 +997,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>479389</v>
+        <v>479392</v>
       </c>
       <c r="R5" t="n">
-        <v>6849588</v>
+        <v>6849592</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>

--- a/artfynd/A 49099-2021 artfynd.xlsx
+++ b/artfynd/A 49099-2021 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124907483</v>
+        <v>124907200</v>
       </c>
       <c r="B2" t="n">
-        <v>79892</v>
+        <v>78810</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>479389</v>
+        <v>479211</v>
       </c>
       <c r="R2" t="n">
-        <v>6849588</v>
+        <v>6849504</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -777,7 +777,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124907200</v>
+        <v>124907602</v>
       </c>
       <c r="B3" t="n">
         <v>78810</v>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>479211</v>
+        <v>479392</v>
       </c>
       <c r="R3" t="n">
-        <v>6849504</v>
+        <v>6849592</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124907602</v>
+        <v>124907483</v>
       </c>
       <c r="B5" t="n">
-        <v>78810</v>
+        <v>79892</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -997,21 +997,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>479392</v>
+        <v>479389</v>
       </c>
       <c r="R5" t="n">
-        <v>6849592</v>
+        <v>6849588</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>

--- a/artfynd/A 49099-2021 artfynd.xlsx
+++ b/artfynd/A 49099-2021 artfynd.xlsx
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124907602</v>
+        <v>124907760</v>
       </c>
       <c r="B3" t="n">
-        <v>78810</v>
+        <v>79891</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,13 +817,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>479392</v>
+        <v>479384</v>
       </c>
       <c r="R3" t="n">
-        <v>6849592</v>
+        <v>6849692</v>
       </c>
       <c r="S3" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124907760</v>
+        <v>124907602</v>
       </c>
       <c r="B4" t="n">
-        <v>79891</v>
+        <v>78810</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,21 +895,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,13 +919,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>479384</v>
+        <v>479392</v>
       </c>
       <c r="R4" t="n">
-        <v>6849692</v>
+        <v>6849592</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>

--- a/artfynd/A 49099-2021 artfynd.xlsx
+++ b/artfynd/A 49099-2021 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124907200</v>
+        <v>124907602</v>
       </c>
       <c r="B2" t="n">
         <v>78810</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>479211</v>
+        <v>479392</v>
       </c>
       <c r="R2" t="n">
-        <v>6849504</v>
+        <v>6849592</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124907760</v>
+        <v>124907200</v>
       </c>
       <c r="B3" t="n">
-        <v>79891</v>
+        <v>78810</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,13 +817,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>479384</v>
+        <v>479211</v>
       </c>
       <c r="R3" t="n">
-        <v>6849692</v>
+        <v>6849504</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124907602</v>
+        <v>124907483</v>
       </c>
       <c r="B4" t="n">
-        <v>78810</v>
+        <v>79892</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,21 +895,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>479392</v>
+        <v>479389</v>
       </c>
       <c r="R4" t="n">
-        <v>6849592</v>
+        <v>6849588</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124907483</v>
+        <v>124907760</v>
       </c>
       <c r="B5" t="n">
-        <v>79892</v>
+        <v>79891</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -997,21 +997,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,13 +1021,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>479389</v>
+        <v>479384</v>
       </c>
       <c r="R5" t="n">
-        <v>6849588</v>
+        <v>6849692</v>
       </c>
       <c r="S5" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>

--- a/artfynd/A 49099-2021 artfynd.xlsx
+++ b/artfynd/A 49099-2021 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124907602</v>
+        <v>124907760</v>
       </c>
       <c r="B2" t="n">
-        <v>78810</v>
+        <v>79891</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,13 +715,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>479392</v>
+        <v>479384</v>
       </c>
       <c r="R2" t="n">
-        <v>6849592</v>
+        <v>6849692</v>
       </c>
       <c r="S2" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -777,7 +777,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124907200</v>
+        <v>124907602</v>
       </c>
       <c r="B3" t="n">
         <v>78810</v>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>479211</v>
+        <v>479392</v>
       </c>
       <c r="R3" t="n">
-        <v>6849504</v>
+        <v>6849592</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124907760</v>
+        <v>124907200</v>
       </c>
       <c r="B5" t="n">
-        <v>79891</v>
+        <v>78810</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -997,21 +997,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,13 +1021,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>479384</v>
+        <v>479211</v>
       </c>
       <c r="R5" t="n">
-        <v>6849692</v>
+        <v>6849504</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>

--- a/artfynd/A 49099-2021 artfynd.xlsx
+++ b/artfynd/A 49099-2021 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124907760</v>
+        <v>124907200</v>
       </c>
       <c r="B2" t="n">
-        <v>79891</v>
+        <v>78810</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,13 +715,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>479384</v>
+        <v>479211</v>
       </c>
       <c r="R2" t="n">
-        <v>6849692</v>
+        <v>6849504</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124907200</v>
+        <v>124907760</v>
       </c>
       <c r="B5" t="n">
-        <v>78810</v>
+        <v>79891</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -997,21 +997,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,13 +1021,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>479211</v>
+        <v>479384</v>
       </c>
       <c r="R5" t="n">
-        <v>6849504</v>
+        <v>6849692</v>
       </c>
       <c r="S5" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>

--- a/artfynd/A 49099-2021 artfynd.xlsx
+++ b/artfynd/A 49099-2021 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124907200</v>
+        <v>124907760</v>
       </c>
       <c r="B2" t="n">
-        <v>78810</v>
+        <v>79891</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,13 +715,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>479211</v>
+        <v>479384</v>
       </c>
       <c r="R2" t="n">
-        <v>6849504</v>
+        <v>6849692</v>
       </c>
       <c r="S2" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124907483</v>
+        <v>124907200</v>
       </c>
       <c r="B4" t="n">
-        <v>79892</v>
+        <v>78810</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,21 +895,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>479389</v>
+        <v>479211</v>
       </c>
       <c r="R4" t="n">
-        <v>6849588</v>
+        <v>6849504</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124907760</v>
+        <v>124907483</v>
       </c>
       <c r="B5" t="n">
-        <v>79891</v>
+        <v>79892</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -997,21 +997,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,13 +1021,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>479384</v>
+        <v>479389</v>
       </c>
       <c r="R5" t="n">
-        <v>6849692</v>
+        <v>6849588</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>

--- a/artfynd/A 49099-2021 artfynd.xlsx
+++ b/artfynd/A 49099-2021 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124907760</v>
+        <v>124907483</v>
       </c>
       <c r="B2" t="n">
-        <v>79891</v>
+        <v>79892</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,13 +715,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>479384</v>
+        <v>479389</v>
       </c>
       <c r="R2" t="n">
-        <v>6849692</v>
+        <v>6849588</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -777,7 +777,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124907602</v>
+        <v>124907200</v>
       </c>
       <c r="B3" t="n">
         <v>78810</v>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>479392</v>
+        <v>479211</v>
       </c>
       <c r="R3" t="n">
-        <v>6849592</v>
+        <v>6849504</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124907200</v>
+        <v>124907760</v>
       </c>
       <c r="B4" t="n">
-        <v>78810</v>
+        <v>79891</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,21 +895,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,13 +919,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>479211</v>
+        <v>479384</v>
       </c>
       <c r="R4" t="n">
-        <v>6849504</v>
+        <v>6849692</v>
       </c>
       <c r="S4" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124907483</v>
+        <v>124907602</v>
       </c>
       <c r="B5" t="n">
-        <v>79892</v>
+        <v>78810</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -997,21 +997,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>479389</v>
+        <v>479392</v>
       </c>
       <c r="R5" t="n">
-        <v>6849588</v>
+        <v>6849592</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>

--- a/artfynd/A 49099-2021 artfynd.xlsx
+++ b/artfynd/A 49099-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>124907483</v>
       </c>
       <c r="B2" t="n">
-        <v>79892</v>
+        <v>80029</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>124907200</v>
       </c>
       <c r="B3" t="n">
-        <v>78810</v>
+        <v>78947</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -882,7 +882,7 @@
         <v>124907760</v>
       </c>
       <c r="B4" t="n">
-        <v>79891</v>
+        <v>80028</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -984,7 +984,7 @@
         <v>124907602</v>
       </c>
       <c r="B5" t="n">
-        <v>78810</v>
+        <v>78947</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>

--- a/artfynd/A 49099-2021 artfynd.xlsx
+++ b/artfynd/A 49099-2021 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124907483</v>
+        <v>124907760</v>
       </c>
       <c r="B2" t="n">
-        <v>80029</v>
+        <v>80028</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,13 +715,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>479389</v>
+        <v>479384</v>
       </c>
       <c r="R2" t="n">
-        <v>6849588</v>
+        <v>6849692</v>
       </c>
       <c r="S2" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -777,7 +777,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124907200</v>
+        <v>124907602</v>
       </c>
       <c r="B3" t="n">
         <v>78947</v>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>479211</v>
+        <v>479392</v>
       </c>
       <c r="R3" t="n">
-        <v>6849504</v>
+        <v>6849592</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124907760</v>
+        <v>124907483</v>
       </c>
       <c r="B4" t="n">
-        <v>80028</v>
+        <v>80029</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,21 +895,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,13 +919,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>479384</v>
+        <v>479389</v>
       </c>
       <c r="R4" t="n">
-        <v>6849692</v>
+        <v>6849588</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -981,7 +981,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124907602</v>
+        <v>124907200</v>
       </c>
       <c r="B5" t="n">
         <v>78947</v>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>479392</v>
+        <v>479211</v>
       </c>
       <c r="R5" t="n">
-        <v>6849592</v>
+        <v>6849504</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
